--- a/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263908312205467</v>
+        <v>1.255426012040775</v>
       </c>
       <c r="C3" t="n">
-        <v>4.671427411980562</v>
+        <v>4.651105234502653</v>
       </c>
       <c r="D3" t="n">
-        <v>6.028161708720554</v>
+        <v>6.101390269980324</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96349743290658</v>
+        <v>12.00792151652375</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.404462758224776</v>
+        <v>1.377574881798344</v>
       </c>
       <c r="C4" t="n">
-        <v>5.242396891571999</v>
+        <v>5.215368731812268</v>
       </c>
       <c r="D4" t="n">
-        <v>6.207576760599333</v>
+        <v>6.331590233625183</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85443641039611</v>
+        <v>12.92453384723579</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.596013246747263</v>
+        <v>1.543614941952383</v>
       </c>
       <c r="C5" t="n">
-        <v>5.989533657842377</v>
+        <v>5.982862302446044</v>
       </c>
       <c r="D5" t="n">
-        <v>6.418355068366622</v>
+        <v>6.630476649607795</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00390197295626</v>
+        <v>14.15695389400622</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.818893222446693</v>
+        <v>1.736951816871136</v>
       </c>
       <c r="C6" t="n">
-        <v>6.906715342787714</v>
+        <v>6.986517230065921</v>
       </c>
       <c r="D6" t="n">
-        <v>6.652389032813751</v>
+        <v>6.900224683928126</v>
       </c>
       <c r="E6" t="n">
-        <v>15.37799759804816</v>
+        <v>15.62369373086518</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.066874442476358</v>
+        <v>1.949418983378824</v>
       </c>
       <c r="C7" t="n">
-        <v>7.96447872414235</v>
+        <v>8.152098503379497</v>
       </c>
       <c r="D7" t="n">
-        <v>6.933962866608239</v>
+        <v>7.194738662894117</v>
       </c>
       <c r="E7" t="n">
-        <v>16.96531603322695</v>
+        <v>17.29625614965244</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.290443417843882</v>
+        <v>1.185163265867421</v>
       </c>
       <c r="C8" t="n">
-        <v>5.552471152425242</v>
+        <v>5.892339792659029</v>
       </c>
       <c r="D8" t="n">
-        <v>5.088117231490047</v>
+        <v>5.443040835736995</v>
       </c>
       <c r="E8" t="n">
-        <v>11.93103180175917</v>
+        <v>12.52054389426345</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.620703390897566</v>
+        <v>1.481380271622639</v>
       </c>
       <c r="C9" t="n">
-        <v>6.837850449754812</v>
+        <v>7.391428624803518</v>
       </c>
       <c r="D9" t="n">
-        <v>5.493669255367761</v>
+        <v>5.864571684755914</v>
       </c>
       <c r="E9" t="n">
-        <v>13.95222309602014</v>
+        <v>14.73738058118207</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.965117058088119</v>
+        <v>1.779542978526144</v>
       </c>
       <c r="C10" t="n">
-        <v>8.289340339015935</v>
+        <v>9.070698797942374</v>
       </c>
       <c r="D10" t="n">
-        <v>5.914638984887826</v>
+        <v>6.352079839399458</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16909638199188</v>
+        <v>17.20232161586798</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.30545753748107</v>
+        <v>2.078258813673862</v>
       </c>
       <c r="C11" t="n">
-        <v>9.937399628091304</v>
+        <v>10.94026671177987</v>
       </c>
       <c r="D11" t="n">
-        <v>6.334093574108031</v>
+        <v>6.852007025573977</v>
       </c>
       <c r="E11" t="n">
-        <v>18.57695073968041</v>
+        <v>19.8705325510277</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.648573729355575</v>
+        <v>2.370044021981942</v>
       </c>
       <c r="C12" t="n">
-        <v>11.6889556796903</v>
+        <v>12.84738273630687</v>
       </c>
       <c r="D12" t="n">
-        <v>6.77008436656413</v>
+        <v>7.367448721085379</v>
       </c>
       <c r="E12" t="n">
-        <v>21.10761377561001</v>
+        <v>22.58487547937419</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.979045228682486</v>
+        <v>2.631258219099586</v>
       </c>
       <c r="C13" t="n">
-        <v>13.54253956552473</v>
+        <v>14.74433645002718</v>
       </c>
       <c r="D13" t="n">
-        <v>7.121794942063865</v>
+        <v>7.820162405715915</v>
       </c>
       <c r="E13" t="n">
-        <v>23.64337973627108</v>
+        <v>25.19575707484268</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.723566087052743</v>
+        <v>1.512362703438127</v>
       </c>
       <c r="C14" t="n">
-        <v>9.581199822487024</v>
+        <v>10.22435256101615</v>
       </c>
       <c r="D14" t="n">
-        <v>5.470612367328587</v>
+        <v>5.965845179258848</v>
       </c>
       <c r="E14" t="n">
-        <v>16.77537827686835</v>
+        <v>17.70256044371312</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.755541609780062</v>
+        <v>1.522906673781737</v>
       </c>
       <c r="C15" t="n">
-        <v>10.48528146585087</v>
+        <v>11.11004606987945</v>
       </c>
       <c r="D15" t="n">
-        <v>5.432775810806914</v>
+        <v>5.975211052357362</v>
       </c>
       <c r="E15" t="n">
-        <v>17.67359888643784</v>
+        <v>18.60816379601855</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.025080441981023</v>
+        <v>1.746057926957038</v>
       </c>
       <c r="C16" t="n">
-        <v>12.46797985943956</v>
+        <v>13.07525953685551</v>
       </c>
       <c r="D16" t="n">
-        <v>5.777202357887822</v>
+        <v>6.380908473660314</v>
       </c>
       <c r="E16" t="n">
-        <v>20.2702626593084</v>
+        <v>21.20222593747286</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.612923120784127</v>
+        <v>1.391077592055476</v>
       </c>
       <c r="C17" t="n">
-        <v>11.50807604161224</v>
+        <v>11.93977995960069</v>
       </c>
       <c r="D17" t="n">
-        <v>5.300583482430081</v>
+        <v>5.887619522184462</v>
       </c>
       <c r="E17" t="n">
-        <v>18.42158264482645</v>
+        <v>19.21847707384063</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.832540082224139</v>
+        <v>1.569647681980928</v>
       </c>
       <c r="C18" t="n">
-        <v>13.47326005615717</v>
+        <v>13.91158095367224</v>
       </c>
       <c r="D18" t="n">
-        <v>5.625885584232262</v>
+        <v>6.295997114720008</v>
       </c>
       <c r="E18" t="n">
-        <v>20.93168572261357</v>
+        <v>21.77722575037317</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.832304462775119</v>
+        <v>1.558445940675472</v>
       </c>
       <c r="C19" t="n">
-        <v>14.43317369146153</v>
+        <v>14.82957396200526</v>
       </c>
       <c r="D19" t="n">
-        <v>5.658764314847487</v>
+        <v>6.374370033950029</v>
       </c>
       <c r="E19" t="n">
-        <v>21.92424246908413</v>
+        <v>22.76238993663076</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.032963876046125</v>
+        <v>1.716291336564274</v>
       </c>
       <c r="C20" t="n">
-        <v>16.58682381279071</v>
+        <v>16.93641435279596</v>
       </c>
       <c r="D20" t="n">
-        <v>6.002061852068513</v>
+        <v>6.735289942462285</v>
       </c>
       <c r="E20" t="n">
-        <v>24.62184954090535</v>
+        <v>25.38799563182252</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.209817513420387</v>
+        <v>1.01177936651972</v>
       </c>
       <c r="C21" t="n">
-        <v>12.15328063284324</v>
+        <v>12.31975559105238</v>
       </c>
       <c r="D21" t="n">
-        <v>4.984195649782462</v>
+        <v>5.614585668156382</v>
       </c>
       <c r="E21" t="n">
-        <v>18.34729379604609</v>
+        <v>18.94612062572848</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255426012040775</v>
+        <v>1.290120975908857</v>
       </c>
       <c r="C3" t="n">
-        <v>4.651105234502653</v>
+        <v>4.619836570122392</v>
       </c>
       <c r="D3" t="n">
-        <v>6.101390269980324</v>
+        <v>6.135054398758947</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00792151652375</v>
+        <v>12.0450119447902</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.377574881798344</v>
+        <v>1.465238597239846</v>
       </c>
       <c r="C4" t="n">
-        <v>5.215368731812268</v>
+        <v>5.100657514552804</v>
       </c>
       <c r="D4" t="n">
-        <v>6.331590233625183</v>
+        <v>6.476780154012393</v>
       </c>
       <c r="E4" t="n">
-        <v>12.92453384723579</v>
+        <v>13.04267626580504</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.543614941952383</v>
+        <v>1.700802360401162</v>
       </c>
       <c r="C5" t="n">
-        <v>5.982862302446044</v>
+        <v>5.720913811614613</v>
       </c>
       <c r="D5" t="n">
-        <v>6.630476649607795</v>
+        <v>6.832661345316521</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15695389400622</v>
+        <v>14.2543775173323</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.736951816871136</v>
+        <v>1.975612782597175</v>
       </c>
       <c r="C6" t="n">
-        <v>6.986517230065921</v>
+        <v>6.480282155410817</v>
       </c>
       <c r="D6" t="n">
-        <v>6.900224683928126</v>
+        <v>7.241644153370688</v>
       </c>
       <c r="E6" t="n">
-        <v>15.62369373086518</v>
+        <v>15.69753909137868</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.949418983378824</v>
+        <v>2.280326148308151</v>
       </c>
       <c r="C7" t="n">
-        <v>8.152098503379497</v>
+        <v>7.352581407716746</v>
       </c>
       <c r="D7" t="n">
-        <v>7.194738662894117</v>
+        <v>7.695131956501669</v>
       </c>
       <c r="E7" t="n">
-        <v>17.29625614965244</v>
+        <v>17.32803951252657</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.185163265867421</v>
+        <v>1.450686896699621</v>
       </c>
       <c r="C8" t="n">
-        <v>5.892339792659029</v>
+        <v>4.974258575550563</v>
       </c>
       <c r="D8" t="n">
-        <v>5.443040835736995</v>
+        <v>6.003629911237101</v>
       </c>
       <c r="E8" t="n">
-        <v>12.52054389426345</v>
+        <v>12.42857538348728</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.481380271622639</v>
+        <v>1.828779399422825</v>
       </c>
       <c r="C9" t="n">
-        <v>7.391428624803518</v>
+        <v>6.069368044374813</v>
       </c>
       <c r="D9" t="n">
-        <v>5.864571684755914</v>
+        <v>6.58632646710712</v>
       </c>
       <c r="E9" t="n">
-        <v>14.73738058118207</v>
+        <v>14.48447391090476</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.779542978526144</v>
+        <v>2.225108369118074</v>
       </c>
       <c r="C10" t="n">
-        <v>9.070698797942374</v>
+        <v>7.314323464060283</v>
       </c>
       <c r="D10" t="n">
-        <v>6.352079839399458</v>
+        <v>7.307241111457341</v>
       </c>
       <c r="E10" t="n">
-        <v>17.20232161586798</v>
+        <v>16.8466729446357</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.078258813673862</v>
+        <v>2.638029865326047</v>
       </c>
       <c r="C11" t="n">
-        <v>10.94026671177987</v>
+        <v>8.674639279754722</v>
       </c>
       <c r="D11" t="n">
-        <v>6.852007025573977</v>
+        <v>8.023917405778134</v>
       </c>
       <c r="E11" t="n">
-        <v>19.8705325510277</v>
+        <v>19.3365865508589</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.370044021981942</v>
+        <v>3.040017854871074</v>
       </c>
       <c r="C12" t="n">
-        <v>12.84738273630687</v>
+        <v>10.08583240734744</v>
       </c>
       <c r="D12" t="n">
-        <v>7.367448721085379</v>
+        <v>8.73715215389975</v>
       </c>
       <c r="E12" t="n">
-        <v>22.58487547937419</v>
+        <v>21.86300241611826</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.631258219099586</v>
+        <v>3.415442704675484</v>
       </c>
       <c r="C13" t="n">
-        <v>14.74433645002718</v>
+        <v>11.56876622698635</v>
       </c>
       <c r="D13" t="n">
-        <v>7.820162405715915</v>
+        <v>9.501272516224628</v>
       </c>
       <c r="E13" t="n">
-        <v>25.19575707484268</v>
+        <v>24.48548144788646</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.512362703438127</v>
+        <v>1.966332659358894</v>
       </c>
       <c r="C14" t="n">
-        <v>10.22435256101615</v>
+        <v>8.149330613320092</v>
       </c>
       <c r="D14" t="n">
-        <v>5.965845179258848</v>
+        <v>7.245818383624711</v>
       </c>
       <c r="E14" t="n">
-        <v>17.70256044371312</v>
+        <v>17.3614816563037</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.522906673781737</v>
+        <v>2.010638933251553</v>
       </c>
       <c r="C15" t="n">
-        <v>11.11004606987945</v>
+        <v>8.805177349665135</v>
       </c>
       <c r="D15" t="n">
-        <v>5.975211052357362</v>
+        <v>7.41915575828653</v>
       </c>
       <c r="E15" t="n">
-        <v>18.60816379601855</v>
+        <v>18.23497204120322</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.746057926957038</v>
+        <v>2.326457352230709</v>
       </c>
       <c r="C16" t="n">
-        <v>13.07525953685551</v>
+        <v>10.37563988224059</v>
       </c>
       <c r="D16" t="n">
-        <v>6.380908473660314</v>
+        <v>8.125130532410411</v>
       </c>
       <c r="E16" t="n">
-        <v>21.20222593747286</v>
+        <v>20.82722776688171</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.391077592055476</v>
+        <v>1.861452552114208</v>
       </c>
       <c r="C17" t="n">
-        <v>11.93977995960069</v>
+        <v>9.573552007870942</v>
       </c>
       <c r="D17" t="n">
-        <v>5.887619522184462</v>
+        <v>7.691639833600231</v>
       </c>
       <c r="E17" t="n">
-        <v>19.21847707384063</v>
+        <v>19.12664439358538</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.569647681980928</v>
+        <v>2.114812182149182</v>
       </c>
       <c r="C18" t="n">
-        <v>13.91158095367224</v>
+        <v>11.14894291392172</v>
       </c>
       <c r="D18" t="n">
-        <v>6.295997114720008</v>
+        <v>8.282003998072007</v>
       </c>
       <c r="E18" t="n">
-        <v>21.77722575037317</v>
+        <v>21.54575909414291</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.558445940675472</v>
+        <v>2.115951009486108</v>
       </c>
       <c r="C19" t="n">
-        <v>14.82957396200526</v>
+        <v>11.89322548346531</v>
       </c>
       <c r="D19" t="n">
-        <v>6.374370033950029</v>
+        <v>8.484548366935167</v>
       </c>
       <c r="E19" t="n">
-        <v>22.76238993663076</v>
+        <v>22.49372485988658</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.716291336564274</v>
+        <v>2.341134480409198</v>
       </c>
       <c r="C20" t="n">
-        <v>16.93641435279596</v>
+        <v>13.60506950292934</v>
       </c>
       <c r="D20" t="n">
-        <v>6.735289942462285</v>
+        <v>9.001841049779856</v>
       </c>
       <c r="E20" t="n">
-        <v>25.38799563182252</v>
+        <v>24.94804503311839</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.01177936651972</v>
+        <v>1.385442360233099</v>
       </c>
       <c r="C21" t="n">
-        <v>12.31975559105238</v>
+        <v>9.985552249435159</v>
       </c>
       <c r="D21" t="n">
-        <v>5.614585668156382</v>
+        <v>7.58952825488152</v>
       </c>
       <c r="E21" t="n">
-        <v>18.94612062572848</v>
+        <v>18.96052286454978</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_41_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.290120975908857</v>
+        <v>2.588946757798709</v>
       </c>
       <c r="C3" t="n">
-        <v>4.619836570122392</v>
+        <v>7.71571927414191</v>
       </c>
       <c r="D3" t="n">
-        <v>6.135054398758947</v>
+        <v>8.252686816680619</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0450119447902</v>
+        <v>18.55735284862124</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.465238597239846</v>
+        <v>1.080102658808869</v>
       </c>
       <c r="C4" t="n">
-        <v>5.100657514552804</v>
+        <v>4.503774277118079</v>
       </c>
       <c r="D4" t="n">
-        <v>6.476780154012393</v>
+        <v>5.868484836233596</v>
       </c>
       <c r="E4" t="n">
-        <v>13.04267626580504</v>
+        <v>11.45236177216054</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.700802360401162</v>
+        <v>1.187266255052578</v>
       </c>
       <c r="C5" t="n">
-        <v>5.720913811614613</v>
+        <v>5.164218834314275</v>
       </c>
       <c r="D5" t="n">
-        <v>6.832661345316521</v>
+        <v>6.150216760194071</v>
       </c>
       <c r="E5" t="n">
-        <v>14.2543775173323</v>
+        <v>12.50170184956092</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.975612782597175</v>
+        <v>1.302665319732338</v>
       </c>
       <c r="C6" t="n">
-        <v>6.480282155410817</v>
+        <v>6.014150650668206</v>
       </c>
       <c r="D6" t="n">
-        <v>7.241644153370688</v>
+        <v>6.545828016078437</v>
       </c>
       <c r="E6" t="n">
-        <v>15.69753909137868</v>
+        <v>13.86264398647898</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.280326148308151</v>
+        <v>1.414984898633052</v>
       </c>
       <c r="C7" t="n">
-        <v>7.352581407716746</v>
+        <v>7.033023220205582</v>
       </c>
       <c r="D7" t="n">
-        <v>7.695131956501669</v>
+        <v>6.927203902233072</v>
       </c>
       <c r="E7" t="n">
-        <v>17.32803951252657</v>
+        <v>15.37521202107171</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.450686896699621</v>
+        <v>1.538435415763679</v>
       </c>
       <c r="C8" t="n">
-        <v>4.974258575550563</v>
+        <v>8.250765913366548</v>
       </c>
       <c r="D8" t="n">
-        <v>6.003629911237101</v>
+        <v>7.294519806188324</v>
       </c>
       <c r="E8" t="n">
-        <v>12.42857538348728</v>
+        <v>17.08372113531855</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.828779399422825</v>
+        <v>1.652448235988394</v>
       </c>
       <c r="C9" t="n">
-        <v>6.069368044374813</v>
+        <v>9.656284039095398</v>
       </c>
       <c r="D9" t="n">
-        <v>6.58632646710712</v>
+        <v>7.710833968755347</v>
       </c>
       <c r="E9" t="n">
-        <v>14.48447391090476</v>
+        <v>19.01956624383914</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.225108369118074</v>
+        <v>1.036450686327443</v>
       </c>
       <c r="C10" t="n">
-        <v>7.314323464060283</v>
+        <v>7.162782162799516</v>
       </c>
       <c r="D10" t="n">
-        <v>7.307241111457341</v>
+        <v>6.060917626938109</v>
       </c>
       <c r="E10" t="n">
-        <v>16.8466729446357</v>
+        <v>14.26015047606507</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.638029865326047</v>
+        <v>0.9678461567546756</v>
       </c>
       <c r="C11" t="n">
-        <v>8.674639279754722</v>
+        <v>7.813170381908944</v>
       </c>
       <c r="D11" t="n">
-        <v>8.023917405778134</v>
+        <v>5.909178701769722</v>
       </c>
       <c r="E11" t="n">
-        <v>19.3365865508589</v>
+        <v>14.69019524043334</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.040017854871074</v>
+        <v>1.047966586898258</v>
       </c>
       <c r="C12" t="n">
-        <v>10.08583240734744</v>
+        <v>9.397514827022446</v>
       </c>
       <c r="D12" t="n">
-        <v>8.73715215389975</v>
+        <v>6.316515641738765</v>
       </c>
       <c r="E12" t="n">
-        <v>21.86300241611826</v>
+        <v>16.76199705565947</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.415442704675484</v>
+        <v>0.8294197304558752</v>
       </c>
       <c r="C13" t="n">
-        <v>11.56876622698635</v>
+        <v>9.074755451774266</v>
       </c>
       <c r="D13" t="n">
-        <v>9.501272516224628</v>
+        <v>5.756958720226254</v>
       </c>
       <c r="E13" t="n">
-        <v>24.48548144788646</v>
+        <v>15.6611339024564</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.966332659358894</v>
+        <v>0.8968265278294614</v>
       </c>
       <c r="C14" t="n">
-        <v>8.149330613320092</v>
+        <v>10.73878835804148</v>
       </c>
       <c r="D14" t="n">
-        <v>7.245818383624711</v>
+        <v>6.09016389104762</v>
       </c>
       <c r="E14" t="n">
-        <v>17.3614816563037</v>
+        <v>17.72577877691856</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.010638933251553</v>
+        <v>0.8671875646382501</v>
       </c>
       <c r="C15" t="n">
-        <v>8.805177349665135</v>
+        <v>11.69563894050859</v>
       </c>
       <c r="D15" t="n">
-        <v>7.41915575828653</v>
+        <v>6.113460764069398</v>
       </c>
       <c r="E15" t="n">
-        <v>18.23497204120322</v>
+        <v>18.67628726921624</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.326457352230709</v>
+        <v>0.945059792539107</v>
       </c>
       <c r="C16" t="n">
-        <v>10.37563988224059</v>
+        <v>13.66971758925399</v>
       </c>
       <c r="D16" t="n">
-        <v>8.125130532410411</v>
+        <v>6.513424778779548</v>
       </c>
       <c r="E16" t="n">
-        <v>20.82722776688171</v>
+        <v>21.12820216057265</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.861452552114208</v>
+        <v>0.5674010856694441</v>
       </c>
       <c r="C17" t="n">
-        <v>9.573552007870942</v>
+        <v>10.21660657162965</v>
       </c>
       <c r="D17" t="n">
-        <v>7.691639833600231</v>
+        <v>5.394104768736632</v>
       </c>
       <c r="E17" t="n">
-        <v>19.12664439358538</v>
+        <v>16.17811242603572</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.114812182149182</v>
+        <v>0.4496208135909543</v>
       </c>
       <c r="C18" t="n">
-        <v>11.14894291392172</v>
+        <v>9.222096147227626</v>
       </c>
       <c r="D18" t="n">
-        <v>8.282003998072007</v>
+        <v>4.884774059773388</v>
       </c>
       <c r="E18" t="n">
-        <v>21.54575909414291</v>
+        <v>14.55649102059197</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.115951009486108</v>
+        <v>0.5230162719604458</v>
       </c>
       <c r="C19" t="n">
-        <v>11.89322548346531</v>
+        <v>11.43888246341692</v>
       </c>
       <c r="D19" t="n">
-        <v>8.484548366935167</v>
+        <v>5.313434559878672</v>
       </c>
       <c r="E19" t="n">
-        <v>22.49372485988658</v>
+        <v>17.27533329525604</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.341134480409198</v>
+        <v>0.5907470460764332</v>
       </c>
       <c r="C20" t="n">
-        <v>13.60506950292934</v>
+        <v>13.85217540008826</v>
       </c>
       <c r="D20" t="n">
-        <v>9.001841049779856</v>
+        <v>5.729253800012409</v>
       </c>
       <c r="E20" t="n">
-        <v>24.94804503311839</v>
+        <v>20.17217624617711</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.385442360233099</v>
+        <v>0.646215791366378</v>
       </c>
       <c r="C21" t="n">
-        <v>9.985552249435159</v>
+        <v>16.36959249827202</v>
       </c>
       <c r="D21" t="n">
-        <v>7.58952825488152</v>
+        <v>6.160839908276349</v>
       </c>
       <c r="E21" t="n">
-        <v>18.96052286454978</v>
+        <v>23.17664819791474</v>
       </c>
     </row>
   </sheetData>
